--- a/design_tables/excel/GameConfig.xlsx
+++ b/design_tables/excel/GameConfig.xlsx
@@ -85,20 +85,6 @@
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="GameConfigTable" displayName="GameConfigTable" ref="A1:F7" headerRowCount="1">
-  <x:tableColumns count="6">
-    <x:tableColumn id="1" name="id"/>
-    <x:tableColumn id="2" name="name"/>
-    <x:tableColumn id="3" name="value"/>
-    <x:tableColumn id="4" name="value_type"/>
-    <x:tableColumn id="5" name="system"/>
-    <x:tableColumn id="6" name="comment"/>
-  </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</x:table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -400,8 +386,5 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf852fa9d5663441e"/>
-  </x:tableParts>
 </x:worksheet>
 </file>
--- a/design_tables/excel/GameConfig.xlsx
+++ b/design_tables/excel/GameConfig.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GameConfig" sheetId="1" r:id="R46fc73a443ba4f8c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GameConfig" sheetId="1" r:id="R6b00b1710bd54c97"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -21,13 +21,13 @@
     <x:font>
       <x:b/>
       <x:sz val="11"/>
-      <x:color rgb="FFFFFF"/>
+      <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
     </x:font>
     <x:font>
       <x:b/>
       <x:sz val="11"/>
-      <x:color rgb="111827"/>
+      <x:color rgb="FF111827"/>
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
@@ -40,17 +40,17 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="1F2937"/>
+        <x:fgColor rgb="FF1F2937"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="374151"/>
+        <x:fgColor rgb="FF374151"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="E5E7EB"/>
+        <x:fgColor rgb="FFE5E7EB"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -266,93 +266,93 @@
     </x:row>
     <x:row r="2" ht="25.5" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>string</x:v>
+        <x:v>default_draw_count</x:v>
       </x:c>
       <x:c r="B2" s="6" t="str">
-        <x:v>string</x:v>
+        <x:v>默认每回合抽牌数量</x:v>
       </x:c>
       <x:c r="C2" s="6" t="str">
-        <x:v>string</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D2" s="6" t="str">
-        <x:v>string</x:v>
+        <x:v>int</x:v>
       </x:c>
       <x:c r="E2" s="6" t="str">
-        <x:v>string</x:v>
+        <x:v>回合系统</x:v>
       </x:c>
       <x:c r="F2" s="6" t="str">
-        <x:v>string</x:v>
+        <x:v>角色表可覆盖该值</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="25.5" customHeight="1">
       <x:c r="A3" s="9" t="str">
-        <x:v>配置ID</x:v>
+        <x:v>default_hand_limit</x:v>
       </x:c>
       <x:c r="B3" s="9" t="str">
-        <x:v>配置名称</x:v>
+        <x:v>默认手牌上限</x:v>
       </x:c>
       <x:c r="C3" s="9" t="str">
-        <x:v>配置值</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D3" s="9" t="str">
-        <x:v>配置类型</x:v>
+        <x:v>int</x:v>
       </x:c>
       <x:c r="E3" s="9" t="str">
-        <x:v>所属系统</x:v>
+        <x:v>牌堆系统</x:v>
       </x:c>
       <x:c r="F3" s="9" t="str">
-        <x:v>说明</x:v>
+        <x:v>角色表可覆盖该值</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="25.5" customHeight="1">
       <x:c r="A4" s="10" t="str">
-        <x:v>default_draw_count</x:v>
+        <x:v>arousal_max</x:v>
       </x:c>
       <x:c r="B4" s="10" t="str">
-        <x:v>默认每回合抽牌数量</x:v>
+        <x:v>发情值上限</x:v>
       </x:c>
       <x:c r="C4" s="10" t="str">
-        <x:v>5</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D4" s="10" t="str">
         <x:v>int</x:v>
       </x:c>
       <x:c r="E4" s="10" t="str">
-        <x:v>回合系统</x:v>
+        <x:v>特殊属性系统</x:v>
       </x:c>
       <x:c r="F4" s="10" t="str">
-        <x:v>角色表可覆盖该值</x:v>
+        <x:v>达到上限时触发高潮状态</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="25.5" customHeight="1">
       <x:c r="A5" s="10" t="str">
-        <x:v>default_hand_limit</x:v>
+        <x:v>human_base_magic_max</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>默认手牌上限</x:v>
+        <x:v>人类形态基础魔力上限</x:v>
       </x:c>
       <x:c r="C5" s="10" t="str">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D5" s="10" t="str">
         <x:v>int</x:v>
       </x:c>
       <x:c r="E5" s="10" t="str">
-        <x:v>牌堆系统</x:v>
+        <x:v>形态系统</x:v>
       </x:c>
       <x:c r="F5" s="10" t="str">
-        <x:v>角色表可覆盖该值</x:v>
+        <x:v>人类形态默认不能使用需要魔力的卡牌</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="25.5" customHeight="1">
       <x:c r="A6" s="10" t="str">
-        <x:v>arousal_max</x:v>
+        <x:v>arousal_card_use_threshold</x:v>
       </x:c>
       <x:c r="B6" s="10" t="str">
-        <x:v>发情值上限</x:v>
+        <x:v>发情反噬阈值</x:v>
       </x:c>
       <x:c r="C6" s="10" t="str">
-        <x:v>100</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D6" s="10" t="str">
         <x:v>int</x:v>
@@ -361,27 +361,27 @@
         <x:v>特殊属性系统</x:v>
       </x:c>
       <x:c r="F6" s="10" t="str">
-        <x:v>达到上限时触发高潮状态</x:v>
+        <x:v>发情值达到该阈值后，玩家每次使用卡牌会额外提升发情值</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="25.5" customHeight="1">
       <x:c r="A7" s="10" t="str">
-        <x:v>human_base_magic_max</x:v>
+        <x:v>arousal_card_use_gain</x:v>
       </x:c>
       <x:c r="B7" s="10" t="str">
-        <x:v>人类形态基础魔力上限</x:v>
+        <x:v>发情反噬增长</x:v>
       </x:c>
       <x:c r="C7" s="10" t="str">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D7" s="10" t="str">
         <x:v>int</x:v>
       </x:c>
       <x:c r="E7" s="10" t="str">
-        <x:v>形态系统</x:v>
+        <x:v>特殊属性系统</x:v>
       </x:c>
       <x:c r="F7" s="10" t="str">
-        <x:v>人类形态默认不能使用需要魔力的卡牌</x:v>
+        <x:v>发情值达到阈值后，每次使用卡牌额外提升的发情值</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
